--- a/data/trans_bre/IP22_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 5,56</t>
+          <t>-11,36; 6,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 2,52</t>
+          <t>-20,31; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 16,54</t>
+          <t>-4,36; 16,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 31,17</t>
+          <t>-13,69; 27,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 50,19</t>
+          <t>-56,22; 60,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,53; 11,97</t>
+          <t>-53,92; 4,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 218,96</t>
+          <t>-31,72; 207,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 276,04</t>
+          <t>-65,83; 255,23</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 3,13</t>
+          <t>-5,37; 3,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -0,34</t>
+          <t>-9,61; -0,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,9</t>
+          <t>-3,98; 3,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,96</t>
+          <t>-4,76; 3,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 15,61</t>
+          <t>-21,83; 18,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,21; -1,19</t>
+          <t>-30,96; 0,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 26,19</t>
+          <t>-21,27; 26,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 33,83</t>
+          <t>-29,27; 28,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 0,8</t>
+          <t>-14,12; 0,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 8,24</t>
+          <t>-7,95; 8,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 7,66</t>
+          <t>-5,39; 7,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 9,79</t>
+          <t>-5,46; 9,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 3,54</t>
+          <t>-47,83; 1,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 39,71</t>
+          <t>-27,48; 38,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 52,34</t>
+          <t>-26,0; 50,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 75,31</t>
+          <t>-25,39; 73,11</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 1,06</t>
+          <t>-5,86; 1,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -0,12</t>
+          <t>-7,96; -0,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,08</t>
+          <t>-2,53; 4,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,95</t>
+          <t>-3,77; 4,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 5,05</t>
+          <t>-25,56; 5,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,11; -0,47</t>
+          <t>-26,79; -0,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 27,05</t>
+          <t>-13,6; 25,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 28,51</t>
+          <t>-22,41; 30,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>-4,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>-28,34%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 6,14</t>
+          <t>-10,96; 6,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 1,19</t>
+          <t>-19,44; 1,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 16,85</t>
+          <t>-4,82; 17,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 27,49</t>
+          <t>-17,34; 6,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 60,54</t>
+          <t>-53,82; 55,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 4,4</t>
+          <t>-52,3; 6,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 207,28</t>
+          <t>-31,18; 252,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 255,23</t>
+          <t>-69,34; 64,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-3,27%</t>
+          <t>-1,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,65</t>
+          <t>-5,31; 3,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,61; -0,02</t>
+          <t>-9,42; 0,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,88</t>
+          <t>-3,98; 3,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,62</t>
+          <t>-4,3; 3,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 18,1</t>
+          <t>-22,34; 17,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 0,3</t>
+          <t>-30,51; 0,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 26,05</t>
+          <t>-20,89; 24,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 28,49</t>
+          <t>-26,4; 31,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 0,13</t>
+          <t>-13,93; 0,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 8,13</t>
+          <t>-7,76; 8,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 7,66</t>
+          <t>-5,48; 7,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 9,89</t>
+          <t>-4,6; 10,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,83; 1,05</t>
+          <t>-47,29; 5,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 38,68</t>
+          <t>-26,87; 38,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 50,55</t>
+          <t>-25,01; 50,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 73,11</t>
+          <t>-22,34; 77,75</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,17</t>
+          <t>-5,66; 1,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,96; -0,11</t>
+          <t>-7,79; -0,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,04</t>
+          <t>-2,54; 3,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,1</t>
+          <t>-3,27; 3,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,56; 5,67</t>
+          <t>-24,38; 5,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,79; -0,46</t>
+          <t>-25,95; 0,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 25,62</t>
+          <t>-13,56; 25,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 30,55</t>
+          <t>-19,78; 23,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han utilizado las urgencias en el último año</t>
+          <t>Menores que han utilizado  algún servicio de urgencias en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-8,58</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,89</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-14,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-27,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-28,34%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.31848176648978</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-8.582626298185975</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.563454359906285</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-4.892413731321161</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1484937846627055</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.2730028528862632</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.4732221645543789</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2834247238119242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-10,96; 6,11</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-19,44; 1,45</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,82; 17,07</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-17,34; 6,23</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-53,82; 55,75</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-52,3; 6,33</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-31,18; 252,59</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-69,34; 64,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-10.96051297571469</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-19.43513759482148</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.817903723863338</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-17.33515816943205</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.538211511426161</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.523044013323836</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3117629721711932</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6933651647751838</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.110916830918037</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.448692804772304</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>17.0727903290867</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.230952789377213</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.5575389209950803</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.06334162869735931</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.52587375509849</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.6470440218179234</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-16,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-1,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,31; 3,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-9,42; 0,23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,98; 3,67</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 3,92</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-22,34; 17,14</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-30,51; 0,96</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-20,89; 24,3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-26,4; 31,98</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.7869383592222473</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-4.709794404472245</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1075801663961956</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.1449114978955696</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.03623826295984141</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1683677819796887</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.006385434534622886</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.01029235440900911</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-6,55</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,84</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-25,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.313307811363729</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-9.424179359446255</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.980199357977701</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.299263385427135</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2233558777873037</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3050878029373779</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2088778317874102</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2640063514684461</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-13,93; 0,86</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,76; 8,02</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,48; 7,61</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,6; 10,31</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-47,29; 5,04</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-26,87; 38,72</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-25,01; 50,74</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-22,34; 77,75</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.41358085258024</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2327276396956182</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.668503314300992</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.924284443344712</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1714053736496932</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.009578254835335502</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.2429940042982429</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3197549134768549</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,42</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,97</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-11,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-14,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-6.553370776676743</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4002601164334901</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.248456187248426</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.842422212219839</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2598118226250493</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.01628922837988028</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.06830639199142799</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1659012010755817</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,66; 1,17</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,79; -0,04</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 3,98</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 3,27</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-24,38; 5,88</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-25,95; 0,04</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-13,56; 25,72</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-19,78; 23,35</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-13.93366667982733</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.75957359640427</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.475090629878947</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.595193754864264</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4729198120403999</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2686904652188952</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2500624553466477</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2233958263913231</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8550760142093303</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.019468196415543</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.608878515258777</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.31289389846181</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.05035241920948247</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3871902295292281</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5073502296764349</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.7774844568565195</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.417105800844163</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.974787486714138</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8793921301998214</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.1905540336655714</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1111313799887241</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1440857332945132</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.05254208755299705</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.01264377532839312</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.657183822981598</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.78695017864578</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.536614228061019</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.274369387362435</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2437967128183356</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2594695614958916</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1356287668745965</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1977866677298249</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.168675837608883</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.04337234275732988</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.97682930800347</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.268248778076216</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.05882542667301124</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.0004283015461458431</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2572264989565686</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2335183403382761</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
